--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260911.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260911.xlsx
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>146,701,085</t>
+          <t>25,280,032</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>25,280,032</t>
+          <t>146,701,085</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>大成鋼</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>107,143,310</t>
+          <t>22,378,317</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>大成鋼</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>22,378,317</t>
+          <t>107,143,310</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
